--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I400"/>
+  <dimension ref="A1:I403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13618,6 +13618,105 @@
       <c r="I400" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>310.58</v>
+      </c>
+      <c r="C401" t="n">
+        <v>352.38</v>
+      </c>
+      <c r="D401" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="E401" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="F401" t="n">
+        <v>363.42</v>
+      </c>
+      <c r="G401" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="H401" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="C402" t="n">
+        <v>354.07</v>
+      </c>
+      <c r="D402" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="E402" t="n">
+        <v>364.55</v>
+      </c>
+      <c r="F402" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="G402" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="H402" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>305.95</v>
+      </c>
+      <c r="C403" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="D403" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="E403" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="F403" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="G403" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="H403" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B420"/>
+  <dimension ref="A1:B423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17835,6 +17934,36 @@
       </c>
       <c r="B420" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -18003,28 +18132,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.150574652136349</v>
+        <v>-0.1560604429978164</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01037718068487137</v>
+        <v>0.01132176988384892</v>
       </c>
       <c r="M2" t="n">
-        <v>9.558161996340155</v>
+        <v>9.511139086695628</v>
       </c>
       <c r="N2" t="n">
-        <v>120.3081163750319</v>
+        <v>119.5258772951757</v>
       </c>
       <c r="O2" t="n">
-        <v>10.96850565824862</v>
+        <v>10.93278909040029</v>
       </c>
       <c r="P2" t="n">
-        <v>315.2053396832706</v>
+        <v>315.2630702369809</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18081,28 +18210,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09367507985665981</v>
+        <v>-0.09389036734189593</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K3" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01250399504000166</v>
+        <v>0.01277285290023888</v>
       </c>
       <c r="M3" t="n">
-        <v>4.826651766939526</v>
+        <v>4.796102170584815</v>
       </c>
       <c r="N3" t="n">
-        <v>39.07520415953939</v>
+        <v>38.78765821879362</v>
       </c>
       <c r="O3" t="n">
-        <v>6.251016250142003</v>
+        <v>6.227973845384517</v>
       </c>
       <c r="P3" t="n">
-        <v>355.7345900528207</v>
+        <v>355.7368404136654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18159,28 +18288,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01166025289487702</v>
+        <v>-0.01108138840386419</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005122865626906448</v>
+        <v>0.0004704496542855541</v>
       </c>
       <c r="M4" t="n">
-        <v>2.974964935985688</v>
+        <v>2.959650184956975</v>
       </c>
       <c r="N4" t="n">
-        <v>14.90511471742299</v>
+        <v>14.80061191232368</v>
       </c>
       <c r="O4" t="n">
-        <v>3.860714275548371</v>
+        <v>3.847156341029525</v>
       </c>
       <c r="P4" t="n">
-        <v>357.4299131653156</v>
+        <v>357.4238276895727</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18237,28 +18366,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05419781931216133</v>
+        <v>0.05841369032013179</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K5" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007105097653588466</v>
+        <v>0.008362812337372016</v>
       </c>
       <c r="M5" t="n">
-        <v>3.763848167773556</v>
+        <v>3.754115136492005</v>
       </c>
       <c r="N5" t="n">
-        <v>22.8760139816488</v>
+        <v>22.7660409849993</v>
       </c>
       <c r="O5" t="n">
-        <v>4.782887619592248</v>
+        <v>4.771377262908405</v>
       </c>
       <c r="P5" t="n">
-        <v>360.8729282700084</v>
+        <v>360.8284097550295</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18315,28 +18444,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0178706554277571</v>
+        <v>-0.01087519850971551</v>
       </c>
       <c r="J6" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K6" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000588223391793985</v>
+        <v>0.0002204744509981538</v>
       </c>
       <c r="M6" t="n">
-        <v>4.500789571253899</v>
+        <v>4.497901189267159</v>
       </c>
       <c r="N6" t="n">
-        <v>30.48863785972672</v>
+        <v>30.42490193316673</v>
       </c>
       <c r="O6" t="n">
-        <v>5.521651732926183</v>
+        <v>5.51587725871114</v>
       </c>
       <c r="P6" t="n">
-        <v>360.0334581648092</v>
+        <v>359.9600290628953</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18393,28 +18522,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04580936431610268</v>
+        <v>-0.04262245227264479</v>
       </c>
       <c r="J7" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K7" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003246736871922007</v>
+        <v>0.002856216210834983</v>
       </c>
       <c r="M7" t="n">
-        <v>4.645763199521156</v>
+        <v>4.626165791732531</v>
       </c>
       <c r="N7" t="n">
-        <v>36.03189558711608</v>
+        <v>35.81436465412875</v>
       </c>
       <c r="O7" t="n">
-        <v>6.00265737712191</v>
+        <v>5.984510393852512</v>
       </c>
       <c r="P7" t="n">
-        <v>346.817807091868</v>
+        <v>346.7842501927412</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18471,28 +18600,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04356476579124489</v>
+        <v>-0.04874915380300825</v>
       </c>
       <c r="J8" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K8" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002755762934216532</v>
+        <v>0.003492816208384264</v>
       </c>
       <c r="M8" t="n">
-        <v>4.537818813424913</v>
+        <v>4.535633640522954</v>
       </c>
       <c r="N8" t="n">
-        <v>38.4121357358499</v>
+        <v>38.28710609051989</v>
       </c>
       <c r="O8" t="n">
-        <v>6.19775247455478</v>
+        <v>6.187657560864199</v>
       </c>
       <c r="P8" t="n">
-        <v>354.7298132856109</v>
+        <v>354.784337176805</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18530,7 +18659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I400"/>
+  <dimension ref="A1:I403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37285,6 +37414,147 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-36.737467748198114,175.81125580076463</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-36.737512727674556,175.81024638643763</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-36.7375625021153,175.80933413823428</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-36.737685719711905,175.80845090108312</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-36.73786250304687,175.80759241332427</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-36.73804578545911,175.8066973600128</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-36.738418260603375,175.80592486273815</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-36.737431641457995,175.811275281917</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-36.73752770069849,175.81024297118495</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-36.73757724286882,175.80933534771648</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-36.73768421569824,175.80845054329083</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-36.737869926585525,175.80759617436502</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-36.738052828712476,175.80670234806263</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-36.73843427998321,175.8059371509466</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-36.737429493230806,175.81127644097813</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-36.73751627158554,175.8102455780939</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-36.737581017939824,175.80933565746201</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-36.73769828264943,175.80845388970164</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-36.73787593214478,175.80759921700525</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-36.73807497582978,175.80671803271426</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-36.738475516465925,175.80596878281824</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I403"/>
+  <dimension ref="A1:I404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13715,6 +13715,39 @@
         <v>354.37</v>
       </c>
       <c r="I403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>303.12</v>
+      </c>
+      <c r="C404" t="n">
+        <v>353.26</v>
+      </c>
+      <c r="D404" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="E404" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="F404" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="G404" t="n">
+        <v>351.22</v>
+      </c>
+      <c r="H404" t="n">
+        <v>354.52</v>
+      </c>
+      <c r="I404" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13731,7 +13764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17963,6 +17996,16 @@
         </is>
       </c>
       <c r="B423" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -18132,28 +18175,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1560604429978164</v>
+        <v>-0.1600990094952934</v>
       </c>
       <c r="J2" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01132176988384892</v>
+        <v>0.0119610576236483</v>
       </c>
       <c r="M2" t="n">
-        <v>9.511139086695628</v>
+        <v>9.505732147412218</v>
       </c>
       <c r="N2" t="n">
-        <v>119.5258772951757</v>
+        <v>119.38284344106</v>
       </c>
       <c r="O2" t="n">
-        <v>10.93278909040029</v>
+        <v>10.92624562423251</v>
       </c>
       <c r="P2" t="n">
-        <v>315.2630702369809</v>
+        <v>315.305669639594</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18210,28 +18253,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09389036734189593</v>
+        <v>-0.09386622279531606</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K3" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01277285290023888</v>
+        <v>0.01283753703940815</v>
       </c>
       <c r="M3" t="n">
-        <v>4.796102170584815</v>
+        <v>4.784304508879154</v>
       </c>
       <c r="N3" t="n">
-        <v>38.78765821879362</v>
+        <v>38.69141682290862</v>
       </c>
       <c r="O3" t="n">
-        <v>6.227973845384517</v>
+        <v>6.220242505152723</v>
       </c>
       <c r="P3" t="n">
-        <v>355.7368404136654</v>
+        <v>355.7365871145108</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18288,28 +18331,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01108138840386419</v>
+        <v>-0.01012547070453727</v>
       </c>
       <c r="J4" t="n">
+        <v>403</v>
+      </c>
+      <c r="K4" t="n">
         <v>402</v>
       </c>
-      <c r="K4" t="n">
-        <v>401</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0004704496542855541</v>
+        <v>0.0003947892852695922</v>
       </c>
       <c r="M4" t="n">
-        <v>2.959650184956975</v>
+        <v>2.956758035209325</v>
       </c>
       <c r="N4" t="n">
-        <v>14.80061191232368</v>
+        <v>14.77299474506907</v>
       </c>
       <c r="O4" t="n">
-        <v>3.847156341029525</v>
+        <v>3.843565368908024</v>
       </c>
       <c r="P4" t="n">
-        <v>357.4238276895727</v>
+        <v>357.4137669794907</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18366,28 +18409,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05841369032013179</v>
+        <v>0.06112112306134995</v>
       </c>
       <c r="J5" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K5" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008362812337372016</v>
+        <v>0.009170993424509444</v>
       </c>
       <c r="M5" t="n">
-        <v>3.754115136492005</v>
+        <v>3.756655355196816</v>
       </c>
       <c r="N5" t="n">
-        <v>22.7660409849993</v>
+        <v>22.78219202791005</v>
       </c>
       <c r="O5" t="n">
-        <v>4.771377262908405</v>
+        <v>4.773069455592497</v>
       </c>
       <c r="P5" t="n">
-        <v>360.8284097550295</v>
+        <v>360.7997457377124</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18444,28 +18487,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01087519850971551</v>
+        <v>-0.007795421871710768</v>
       </c>
       <c r="J6" t="n">
+        <v>403</v>
+      </c>
+      <c r="K6" t="n">
         <v>402</v>
       </c>
-      <c r="K6" t="n">
-        <v>401</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0002204744509981538</v>
+        <v>0.000113577661568498</v>
       </c>
       <c r="M6" t="n">
-        <v>4.497901189267159</v>
+        <v>4.500208148340048</v>
       </c>
       <c r="N6" t="n">
-        <v>30.42490193316673</v>
+        <v>30.44471697313544</v>
       </c>
       <c r="O6" t="n">
-        <v>5.51587725871114</v>
+        <v>5.517673148450843</v>
       </c>
       <c r="P6" t="n">
-        <v>359.9600290628953</v>
+        <v>359.9276154566885</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18522,28 +18565,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04262245227264479</v>
+        <v>-0.03984917199270162</v>
       </c>
       <c r="J7" t="n">
+        <v>403</v>
+      </c>
+      <c r="K7" t="n">
         <v>402</v>
       </c>
-      <c r="K7" t="n">
-        <v>401</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.002856216210834983</v>
+        <v>0.002506263812279808</v>
       </c>
       <c r="M7" t="n">
-        <v>4.626165791732531</v>
+        <v>4.627781987055518</v>
       </c>
       <c r="N7" t="n">
-        <v>35.81436465412875</v>
+        <v>35.80213328086739</v>
       </c>
       <c r="O7" t="n">
-        <v>5.984510393852512</v>
+        <v>5.983488387292766</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7842501927412</v>
+        <v>346.7549839674364</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18600,28 +18643,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04874915380300825</v>
+        <v>-0.0482273003809706</v>
       </c>
       <c r="J8" t="n">
+        <v>403</v>
+      </c>
+      <c r="K8" t="n">
         <v>402</v>
       </c>
-      <c r="K8" t="n">
-        <v>401</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003492816208384264</v>
+        <v>0.003437759039475741</v>
       </c>
       <c r="M8" t="n">
-        <v>4.535633640522954</v>
+        <v>4.526755199271283</v>
       </c>
       <c r="N8" t="n">
-        <v>38.28710609051989</v>
+        <v>38.19458601065754</v>
       </c>
       <c r="O8" t="n">
-        <v>6.187657560864199</v>
+        <v>6.180176859173008</v>
       </c>
       <c r="P8" t="n">
-        <v>354.784337176805</v>
+        <v>354.7788300955569</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18659,7 +18702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I403"/>
+  <dimension ref="A1:I404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37555,6 +37598,53 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-36.737406110603565,175.81128905690898</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-36.73752052427874,175.81024460808135</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-36.73758757937277,175.80933619582936</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-36.73771323431434,175.80845744658006</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-36.73788310545154,175.80760285127067</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-36.73808522767474,175.80672529310385</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-36.73847666618183,175.80596966474823</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0162/nzd0162.xlsx
+++ b/data/nzd0162/nzd0162.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I404"/>
+  <dimension ref="A1:I405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13745,11 +13745,44 @@
         <v>351.22</v>
       </c>
       <c r="H404" t="n">
-        <v>354.52</v>
+        <v>354.41</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>298.31</v>
+      </c>
+      <c r="C405" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="D405" t="n">
+        <v>358.35</v>
+      </c>
+      <c r="E405" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="F405" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="G405" t="n">
+        <v>353.24</v>
+      </c>
+      <c r="H405" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13764,7 +13797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18007,6 +18040,16 @@
       </c>
       <c r="B424" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -18175,28 +18218,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1600990094952934</v>
+        <v>-0.166544039248422</v>
       </c>
       <c r="J2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0119610576236483</v>
+        <v>0.01296262000858128</v>
       </c>
       <c r="M2" t="n">
-        <v>9.505732147412218</v>
+        <v>9.511094681477495</v>
       </c>
       <c r="N2" t="n">
-        <v>119.38284344106</v>
+        <v>119.4833714226247</v>
       </c>
       <c r="O2" t="n">
-        <v>10.92624562423251</v>
+        <v>10.93084495465125</v>
       </c>
       <c r="P2" t="n">
-        <v>315.305669639594</v>
+        <v>315.3739579195046</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18253,28 +18296,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09386622279531606</v>
+        <v>-0.09613005758602819</v>
       </c>
       <c r="J3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01283753703940815</v>
+        <v>0.01351360020518744</v>
       </c>
       <c r="M3" t="n">
-        <v>4.784304508879154</v>
+        <v>4.785495349196493</v>
       </c>
       <c r="N3" t="n">
-        <v>38.69141682290862</v>
+        <v>38.64719111686711</v>
       </c>
       <c r="O3" t="n">
-        <v>6.220242505152723</v>
+        <v>6.216686506240049</v>
       </c>
       <c r="P3" t="n">
-        <v>355.7365871145108</v>
+        <v>355.7604456578125</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18331,28 +18374,28 @@
         <v>0.1265</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01012547070453727</v>
+        <v>-0.009526484631184965</v>
       </c>
       <c r="J4" t="n">
+        <v>404</v>
+      </c>
+      <c r="K4" t="n">
         <v>403</v>
       </c>
-      <c r="K4" t="n">
-        <v>402</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0003947892852695922</v>
+        <v>0.0003513841826624509</v>
       </c>
       <c r="M4" t="n">
-        <v>2.956758035209325</v>
+        <v>2.952188506275759</v>
       </c>
       <c r="N4" t="n">
-        <v>14.77299474506907</v>
+        <v>14.73992998789273</v>
       </c>
       <c r="O4" t="n">
-        <v>3.843565368908024</v>
+        <v>3.839261646188331</v>
       </c>
       <c r="P4" t="n">
-        <v>357.4137669794907</v>
+        <v>357.4074340271771</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18409,28 +18452,28 @@
         <v>0.065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06112112306134995</v>
+        <v>0.06380502331159434</v>
       </c>
       <c r="J5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K5" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009170993424509444</v>
+        <v>0.0100113701531257</v>
       </c>
       <c r="M5" t="n">
-        <v>3.756655355196816</v>
+        <v>3.759102461954576</v>
       </c>
       <c r="N5" t="n">
-        <v>22.78219202791005</v>
+        <v>22.79679234968313</v>
       </c>
       <c r="O5" t="n">
-        <v>4.773069455592497</v>
+        <v>4.774598658492998</v>
       </c>
       <c r="P5" t="n">
-        <v>360.7997457377124</v>
+        <v>360.7712018698061</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18487,28 +18530,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.007795421871710768</v>
+        <v>-0.005097735148455513</v>
       </c>
       <c r="J6" t="n">
+        <v>404</v>
+      </c>
+      <c r="K6" t="n">
         <v>403</v>
       </c>
-      <c r="K6" t="n">
-        <v>402</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.000113577661568498</v>
+        <v>4.873314399789219e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.500208148340048</v>
+        <v>4.500712341663053</v>
       </c>
       <c r="N6" t="n">
-        <v>30.44471697313544</v>
+        <v>30.44204740977899</v>
       </c>
       <c r="O6" t="n">
-        <v>5.517673148450843</v>
+        <v>5.517431232899871</v>
       </c>
       <c r="P6" t="n">
-        <v>359.9276154566885</v>
+        <v>359.899093388922</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18565,28 +18608,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03984917199270162</v>
+        <v>-0.03608847392762086</v>
       </c>
       <c r="J7" t="n">
+        <v>404</v>
+      </c>
+      <c r="K7" t="n">
         <v>403</v>
       </c>
-      <c r="K7" t="n">
-        <v>402</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.002506263812279808</v>
+        <v>0.002060105724970618</v>
       </c>
       <c r="M7" t="n">
-        <v>4.627781987055518</v>
+        <v>4.634030706403846</v>
       </c>
       <c r="N7" t="n">
-        <v>35.80213328086739</v>
+        <v>35.85386385164988</v>
       </c>
       <c r="O7" t="n">
-        <v>5.983488387292766</v>
+        <v>5.987809603824247</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7549839674364</v>
+        <v>346.7151171316393</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18643,28 +18686,28 @@
         <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0482273003809706</v>
+        <v>-0.04727839282266325</v>
       </c>
       <c r="J8" t="n">
+        <v>404</v>
+      </c>
+      <c r="K8" t="n">
         <v>403</v>
       </c>
-      <c r="K8" t="n">
-        <v>402</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003437759039475741</v>
+        <v>0.003322258589376847</v>
       </c>
       <c r="M8" t="n">
-        <v>4.526755199271283</v>
+        <v>4.519835369049764</v>
       </c>
       <c r="N8" t="n">
-        <v>38.19458601065754</v>
+        <v>38.10928410257744</v>
       </c>
       <c r="O8" t="n">
-        <v>6.180176859173008</v>
+        <v>6.173271750261561</v>
       </c>
       <c r="P8" t="n">
-        <v>354.7788300955569</v>
+        <v>354.7687681749216</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18702,7 +18745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I404"/>
+  <dimension ref="A1:I405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37636,12 +37679,59 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>-36.73847666618183,175.80596966474823</t>
+          <t>-36.73847582305683,175.80596901799956</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-36.73736636839715,175.81131049951676</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-36.73747941491096,175.8102539848655</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-36.73758119770511,175.8093356722118</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-36.73771314584295,175.80845742553345</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-36.73787701648186,175.8075997663709</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-36.738101035862094,175.80673648851769</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-36.73848410101124,175.80597536789625</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
